--- a/GearSage-client/pkgGear/data_raw/nories_rod_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/nories_rod_import.xlsx
@@ -27,7 +27,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +44,16 @@
         <fgColor rgb="FFE8F1FB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F6FA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -57,10 +67,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -436,7 +448,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -486,50 +498,55 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>fit_style_tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>images</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>series_positioning</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>main_selling_points</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>official_reference_price</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>market_status</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>player_positioning</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>player_selling_points</t>
         </is>
@@ -566,40 +583,45 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>bass</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>https://static.gearsage.club/gearsage/Gearimg/images/nories_rods/NR1000_Road_Runner_VOICE_LTT.jpg</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Fresh Water / Bass</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>ハードベイトとソフトベイト、どちらもハイレベルに使いこなせる「ロードランナー ヴォイス」オリジナルラインナップ。その優れたブランクスを受け継ぎ、セッティングバランスをリファインすることでさらにテクニカルな攻め込みを可能にしています。 「超えられるはずのないヴォイスの性能を、超えてしまった」と田辺哲男自身が驚愕した「本当に釣れる」性能。もっとタイトに、もっとダイレクトに、よりパーフェクトに…。 「ロードランナーヴォイスLTT」が、あなたを</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>¥56,000 / ¥57,000 / ¥58,000</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>官网展示</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>ハードベイトとソフトベイト、どちらもハイレベルに使いこなせる「ロードランナー ヴォイス」オリジナルラインナップ。その優れたブランクスを受け継ぎ、セッティングバランスをリファインすることでさらにテクニカルな攻め込みを可能にしています。 「超えられるはずのないヴォイスの性能を、超えてしまった」と田辺哲男自身が驚愕した「本当に釣れる」性能。もっとタイトに、もっとダイレクトに、よりパーフェクトに…。 「ロードランナーヴォイスLTT」が、あなたを新たなバスフィッシングの世界へ導きます。</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>淡水 Bass / Versatile</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Road Runner 泛用竿系 / 硬餌、軟餌與 power game 番手覆蓋完整</t>
         </is>
@@ -636,30 +658,35 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>bass</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>https://static.gearsage.club/gearsage/Gearimg/images/nories_rods/NR1001_Road_Runner_VOICE_HARD_BAIT_SPECIAL.jpg</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Fresh Water / Bass</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>田辺哲男は言う「ハードベイトロッドのキモは“キャスト”だ」。  目指したのは極限精度のハードベイトゲームを実現するキャスティングアキュラシー。自分のルアーのアピール力、ルアーに気付かせられる距離、バスのポジション、向き、追わせる方向までも考え合わせたトレースラインで、バイトさせるべきポジションで狙い通りにバイトさせるキャスト。狙い澄ました一投で決める、究極の攻め込みを実現できるキャスティングパフォーマンスを誇るのが「ロードランナーヴォイ</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>¥63,000 / ¥61,000 / ¥64,000 / ¥70,000 / ¥55,000 / ¥56,000 / ¥57,000 / ¥58,000 / ¥59,000</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>官网展示</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>田辺哲男は言う「ハードベイトロッドのキモは“キャスト”だ」。
 目指したのは極限精度のハードベイトゲームを実現するキャスティングアキュラシー。自分のルアーのアピール力、ルアーに気付かせられる距離、バスのポジション、向き、追わせる方向までも考え合わせたトレースラインで、バイトさせるべきポジションで狙い通りにバイトさせるキャスト。狙い澄ました一投で決める、究極の攻め込みを実現できるキャスティングパフォーマンスを誇るのが「ロードランナーヴォイス ハードベイトスペシャル」。
@@ -667,12 +694,12 @@
 ハードベイトエキスパートへの近道は、ハードベイトスペシャルが知っている。</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>淡水 Bass / Hard bait</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>硬餌專用竿系 / cast accuracy、巻物節奏與咬口追従性是核心</t>
         </is>
@@ -709,40 +736,45 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>bass</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>https://static.gearsage.club/gearsage/Gearimg/images/nories_rods/NR1002_Road_Runner_STRUCTURE_NXS.jpg</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Fresh Water / Bass</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>「ロードランナー」ブランクをパーツのセッティングによってソフトベイト特化型とした初代「ストラクチャー」を、さらなる特化を進めNEXT STAGEシリーズとしたのが「ロードランナー ストラクチャーNXS」。 ブランクの基本構成は「ロードランナー」ならではのトルク感を失うことなく、ソフトベイト専用と割り切るからこそ可能なチューニングを施し、張りと感度を大幅に向上。軽量化が難しいとされるトルク重視型ブランクでありながら軽さをも両立し、高い操作</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>¥61,000 / ¥56,000 / ¥55,000 / ¥57,000 / ¥59,000 / ¥60,000 / ¥58,000</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>官网展示</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>「ロードランナー」ブランクをパーツのセッティングによってソフトベイト特化型とした初代「ストラクチャー」を、さらなる特化を進めNEXT STAGEシリーズとしたのが「ロードランナー ストラクチャーNXS」。 ブランクの基本構成は「ロードランナー」ならではのトルク感を失うことなく、ソフトベイト専用と割り切るからこそ可能なチューニングを施し、張りと感度を大幅に向上。軽量化が難しいとされるトルク重視型ブランクでありながら軽さをも両立し、高い操作性を実現しています。 ルアー自体のパワーはハードルアーに比べ「弱い」位置づけのソフトベイト。しかしながらそれで無ければ喰わせられないシチュエーションがあるのは周知の事実。ソフトベイトゲームをとりあえず釣るための「守りの釣り」にすることなく、ビッグフィッシュを狙う「攻めのスローダウン」として繰り出すアングラーならば、間違いなく手放せなくなるパートナー。それが「ロードランナー ストラクチャーNXS」です。</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>淡水 Bass / Soft bait structure</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>軟餌與 structure 攻略竿系 / Texas、jig、neko、finesse 等番手分工清楚</t>
         </is>
@@ -779,40 +811,45 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>bass</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>https://static.gearsage.club/gearsage/Gearimg/images/nories_rods/NR1003_Road_Runner_VOICE_JUNGLE.jpg</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Fresh Water / Bass</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>バスアングラーならば誰しも「記憶に残る一匹」との出会いがあるだろう。 自己最大魚、追い続けて出会えた一匹、勝利を決めた一匹……。 どんなアングラーの、そのどれもに共通するのは「そのワンキャストをした」こと。 そのワンキャストがどれだけの感動をもたらし、その日の記憶をどれだけ深く刻みこむかは、キャストしなければ分からない。 バスフィッシングにおいて欠くことのできない要素、“ヘビーカバー”。 並みのタックルではルアーを撃ち込む気にすらならな</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>¥58,000 / ¥59,000 / ¥62,000 / ¥63,000</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>官网展示</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>バスアングラーならば誰しも「記憶に残る一匹」との出会いがあるだろう。 自己最大魚、追い続けて出会えた一匹、勝利を決めた一匹……。 どんなアングラーの、そのどれもに共通するのは「そのワンキャストをした」こと。 そのワンキャストがどれだけの感動をもたらし、その日の記憶をどれだけ深く刻みこむかは、キャストしなければ分からない。 バスフィッシングにおいて欠くことのできない要素、“ヘビーカバー”。 並みのタックルではルアーを撃ち込む気にすらならない難攻不落なスポットへ、記憶に残るかもしれないキャストを撃ち込めるのがフリッピンロッド。 そのワンキャストが撃てることと、撃てないこと。それがどれほど大きな差を生むことになるかは、あなたの記憶に刻まれているだろう。 「ロードランナー ヴォイス ジャングル」は、そのどれもがビッグフィッシュと、ヘビーカバーと戦う強さを持ちながらも、 狡猾なビッグフィッシュに口を使わせる繊細なルアー操作性と、バイトを弾かない一瞬のタワミ、強引かつしなやかにランディングできる強靭なトルクを併せ持つ。 後悔しないために、記憶に残るワンキャストを撃ち込めるロッド達、それが「ロードランナーヴォイス ジャングル」。</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>淡水 Bass / Heavy cover</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Heavy cover 與 power finesse 竿系 / 太線、障礙區控魚和強力打撃取向明確</t>
         </is>

--- a/GearSage-client/pkgGear/data_raw/nories_rod_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/nories_rod_import.xlsx
@@ -454,7 +454,7 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="48" customWidth="1" min="14" max="14"/>
     <col width="90" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
@@ -866,7 +866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR56"/>
+  <dimension ref="A1:AS56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -911,7 +911,7 @@
     <col width="24" customWidth="1" min="40" max="40"/>
     <col width="90" customWidth="1" min="41" max="41"/>
     <col width="16" customWidth="1" min="42" max="42"/>
-    <col width="16" customWidth="1" min="43" max="43"/>
+    <col width="48" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1127,10 +1127,15 @@
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
+          <t>product_technical</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
           <t>Extra Spec 1</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Extra Spec 2</t>
         </is>
@@ -1275,8 +1280,13 @@
           <t>根がかりをスムーズにかわし、ルアーをシャープに操れる強いティップを持ちながら、パラボリックな調子でルアーウエイトに関係なく投げやすいバーサタイル性を持つアイテム。ショートレングスでの正確なキャストから抵抗の大きな大型トップウォーターまでも機敏に動かす。バルキーベイトのネコリグでオーバーハング絡みのカバーを撃つ。ディープでメタルジグやフットボールジグを操る。バイブレーションやチャター系などのバラシの多い重いルアーを使う場面でも高いランディング率を誇り、完成度の高いゲームを展開できます。</t>
         </is>
       </c>
-      <c r="AQ2" s="1" t="inlineStr"/>
+      <c r="AQ2" s="1" t="inlineStr">
+        <is>
+          <t>富士工業製ステンレスフレームSICガイド / Kガイド / MNSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR2" s="1" t="inlineStr"/>
+      <c r="AS2" s="1" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1417,8 +1427,13 @@
           <t>難しいキャストもこなせるレングスに、ルアー対応幅が広いテーパーで高度な汎用性を備えたアイテム。小型クランクベイトやレイダウンミノーウエイク110プロップなどの空気抵抗の大きなトップウォーターでもしっかりとキャストでき、ルアーをバスに吸い込ませる柔らかなティップ。それでいて細身ソフトルアーに1/0、2/0フックのライトテキサス、ノーシンカーシャッドテールなど3/0フックまでのフッキングにも十分なバットパワーを持っています。クリアリザーバーからマディーシャローレイクまで、どんな場所でも活躍するライト系オールラウンダーです。</t>
         </is>
       </c>
-      <c r="AQ3" s="1" t="inlineStr"/>
+      <c r="AQ3" s="1" t="inlineStr">
+        <is>
+          <t>富士工業製ステンレスフレームSICガイド / Kガイド / MNSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR3" s="1" t="inlineStr"/>
+      <c r="AS3" s="1" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1559,8 +1574,13 @@
           <t>テキサスリグやラバージグで極限の精度でピッチングを続けることができるエキスパートアイテム。障害物を不自然に揺らすことなく、リグを跳ばすことなく抜いてこられる硬めのティップ。ベリーからバットの強い反発力で強いフッキングと近距離でもバラシの少ないランディングを可能にします。同時にこの強さでも軽いフロッグを正確にサイドハンドキャストでき、ティップの向きを自由に使える操作性でカバー攻めフロッグに最高のマッチング。オーバーハングの中の小さなシェードに撃ち込む。倒木の隙間のバンクにぶつけて着水させる。泳ぎ出しをも調整できるタイトなフロッグゲームを展開できます。</t>
         </is>
       </c>
-      <c r="AQ4" s="1" t="inlineStr"/>
+      <c r="AQ4" s="1" t="inlineStr">
+        <is>
+          <t>富士工業製ステンレスフレームSICガイド / Kガイド / MNSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR4" s="1" t="inlineStr"/>
+      <c r="AS4" s="1" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1701,8 +1721,13 @@
           <t>ショットシャロースクエアやショットオーバー3、3/8oz.∼1/2oz.スピナーベイト、ビッグミノーのジャーキングなどでオープンエリアを流していく。ヘビーダウンショットやベイトネコなどで杭周りなどライトカバーを手返し良く撃っていく。使い勝手の良いレングスと柔らかめでありながらトルクフルなブランクでライト系のあらゆるルアーをこなせる汎用性の高いアイテム。12lb.程度のラインとセットしておけばどんなレイクでも活躍できる状況対応力が手に入ります。メタルワサビー8ｇでのライトメタル、オープンウォーターでのフラチャットまでもこなすライト系マルチパーパスアイテムです。</t>
         </is>
       </c>
-      <c r="AQ5" s="1" t="inlineStr"/>
+      <c r="AQ5" s="1" t="inlineStr">
+        <is>
+          <t>富士工業製ステンレスフレームSICガイド / Kガイド / MNSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR5" s="1" t="inlineStr"/>
+      <c r="AS5" s="1" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1843,8 +1868,13 @@
           <t>3/8oz.以上のスピナーベイトやバイブレーション、中型クランクを一通りこなせる強さと素直なテーパーで、下に捌くジャーキングなどもこなせるレングスのアイテム。もちろんベリーからの力強いトルクがあるので、テキサスリグやヘビダンのフッキングもしっかりと決めることができます。ややソフトベイト向きな「630MH」に比べ、ティップ部を長めに取ってあるのでハードベイトに幅広く対応。トルクフルなブランクならではの使い回しを誇ります。</t>
         </is>
       </c>
-      <c r="AQ6" s="1" t="inlineStr"/>
+      <c r="AQ6" s="1" t="inlineStr">
+        <is>
+          <t>富士工業製ステンレスフレームSICガイド / Kガイド / MNSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR6" s="1" t="inlineStr"/>
+      <c r="AS6" s="1" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1985,8 +2015,13 @@
           <t>ティップからしっかりとした強さを持つ強靭なムチのようなアイテム。ガチガチではないのでキャスティングもしやすく、ロングディスタンスでバスを掛けてもバラシにくい。1/2∼3/4oz.のスピナーベイトでウィードを切りながらのスローロールや、ハスやガマなどの硬いベジテーションを弾きながら引くシャロー攻めにも最適。6/0フックのテキサスリグやガンタージグなどのガード付きラバージグでもフッキングをしっかり決める。ダイラッカをきっちりとリフトして太軸トリプルフックを全体パワーで掛ける。トルクの強いブランクを堪能できる一本。</t>
         </is>
       </c>
-      <c r="AQ7" s="1" t="inlineStr"/>
+      <c r="AQ7" s="1" t="inlineStr">
+        <is>
+          <t>富士工業製ステンレスフレームSICガイド / Kガイド / MNSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR7" s="1" t="inlineStr"/>
+      <c r="AS7" s="1" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2127,8 +2162,13 @@
           <t>チャター系ベイトやスイミングジグ、バズベイトでのロッドを立てたスラックラインリーリングで素晴らしい操作性を見せる。ロングキャストテキサスのズル引きやボトムバンピングもしやすい。長めかつ軽快な、レングスを活かした攻めが得意なアイテム。もちろんカバーロッドとしても秀逸で、4/0フックまでのテキサスリグなどでディスタンスをとってアプローチし、ラインスラックが多い状態からでもロングストロークで確実にフックアップ可能です。</t>
         </is>
       </c>
-      <c r="AQ8" s="1" t="inlineStr"/>
+      <c r="AQ8" s="1" t="inlineStr">
+        <is>
+          <t>富士工業製ステンレスフレームSICガイド / Kガイド / MNSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR8" s="1" t="inlineStr"/>
+      <c r="AS8" s="1" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -2269,8 +2309,13 @@
           <t>ヒラクランクギルやベジテーションシリーズなどの大型ボディーのプラグでもフッキングを決める強さと、それらをスラックラインで巻くためのレングスを持つアイテム。ソフトベイトでは1/4oz.シンカーのテキサスリグやチェリーリグでのエスケープツイン。5/0フックのノーシンカーフリップギル、ガード付きラバージグも、強く、繊細にこなせるアイテム。16lbラインとの組み合わせでテクニカルなヘビー系の攻めが可能になります。</t>
         </is>
       </c>
-      <c r="AQ9" s="1" t="inlineStr"/>
+      <c r="AQ9" s="1" t="inlineStr">
+        <is>
+          <t>富士工業製ステンレスフレームSICガイド / Kガイド / MNSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR9" s="1" t="inlineStr"/>
+      <c r="AS9" s="1" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -2411,8 +2456,13 @@
           <t>ブランク全体でヘビーパワーを発生するのが「パラボリックヘビー」。最小限の力でボリュームのあるルアー達を思い通りに操れ、パラボリックな調子なのに太軸フックでもしっかりとフッキングを決められる。そして何より魚をバラさない調子は新感覚のバランス。6’9”という長さは、あるときはロングキャスト、必要であればピンポイントシュートキャスト、そしてピッチングと、バーサタイルな使用を前提とした長さ。スローダウンのジグから、巻き中心のビッグクランクや大型スピナーベイトまで、ソフトベイトからハードベイトまでを実に気持ち良く使いこなせる1本です。</t>
         </is>
       </c>
-      <c r="AQ10" s="1" t="inlineStr"/>
+      <c r="AQ10" s="1" t="inlineStr">
+        <is>
+          <t>富士工業製ステンレスフレームSICガイド / Kガイド / MNSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR10" s="1" t="inlineStr"/>
+      <c r="AS10" s="1" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -2553,8 +2603,13 @@
           <t>ロードランナー誕生から長きに渡りパワーゲームエキスパートに支持され続ける名竿をベースとするアイテム。3/4oz.前後の「クリスタルS」を使ったスローローリングでは、ロッドストロークを活かしたスウィープスイミングで水深3∼5mをきっちり探り、小さなバイトも弾かず、かつ確実にフックアップ。そのアドバンテージは大型スイムベイトやビッグスプーンにハイレベル対応。その一方でソフトベイト用としても6/0フックテキサスリグやガード付きジグでのヘビーカバー撃ち、クリアディープでのヘビキャロまで活躍。あらゆる釣り方をこなせる深いポテンシャルを持つ1本です。</t>
         </is>
       </c>
-      <c r="AQ11" s="1" t="inlineStr"/>
+      <c r="AQ11" s="1" t="inlineStr">
+        <is>
+          <t>富士工業製ステンレスフレームSICガイド / Kガイド / MNSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR11" s="1" t="inlineStr"/>
+      <c r="AS11" s="1" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2695,8 +2750,13 @@
           <t>グラスならではの張りの弱いティップ。柔らかく、トルクがスムースに立ち上がるベリー。芯の強さを持たせたバット。グラスメインの6’6”とは思えぬ取り回しの良さと軽快さ、素直なテーパーが光る田辺哲男監修のアイテム。軽量クランクベイトから1/2ozブレーデッドジグまで、バズベイト、スピナーベイトはもちろんのこと、操作系のトップウォーターやジャークベイトもこなせる対応幅の広さを誇り、さらに難しい角度からのオーバーハング撃ちも躊躇なく繰り出せる優れたキャストバランスをも持ち合わせます。グラスならではの追従性で、タフコンディション下でもバイトを増やしバラさない、完成度の高いハードベイトゲームを可能にします。チタンフレームガイド採用。</t>
         </is>
       </c>
-      <c r="AQ12" s="2" t="inlineStr"/>
+      <c r="AQ12" s="2" t="inlineStr">
+        <is>
+          <t>バリアブルテーパー / グラスコンポジット（-Gc） / バキューム / チタンフレームガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR12" s="2" t="inlineStr"/>
+      <c r="AS12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2837,8 +2897,13 @@
           <t>伊藤巧プロデュースの「エリートスペック」アイテム。小型∼3ｍダイバークランク、10ｇ前後のシャッドにも対応するリーリングスペシャル。しなやかで柔らかいブランクで、ルアーの持つ「釣れる動き」を最大限引き出すリトリーブが可能。ライトプラグもストレスなくキャストできる柔らかさを持たせながらも、クランクベイトをカバー下に滑り込ませられるティップの張りをガイドセッティングで獲得。もちろんグラスならではのバイト追従性で、ショートバイトが多発するようなタフコンディション下でも絡め取るようなフッキングを可能にします。コンポジットブランクでありながら、グラスらしい柔軟さとその利点を存分に感じられるアイテムです。ステンレスフレームでオールダブルフットガイドを採用。</t>
         </is>
       </c>
-      <c r="AQ13" s="2" t="inlineStr"/>
+      <c r="AQ13" s="2" t="inlineStr">
+        <is>
+          <t>バリアブルテーパー / グラスコンポジット（-Gc） / バキューム / ステンレスフレームオールダブルフットガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR13" s="2" t="inlineStr"/>
+      <c r="AS13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2979,8 +3044,13 @@
           <t>伊藤巧プロデュースの「エリートスペック」アイテム。スピナーベイトやブレーデッドジグ、中型クランクベイトなど、巻き抵抗の大きなルアーをきっちり使えるファストテーパーな6’10”ブランク。重いルアーでラインが張り気味のリトリーブからでも、バイトにはしっかりと吸い込ませるグラスならではの柔軟性を持ちながらも、ビッグバスの上顎に大きなシングルフックを叩き込めるバットの強さを誇ります。同時にグラスの弱点であるキャストのダルさをも軽減し、6’10”を感じさせないシャープなキャスティングを可能としています。ガイドはブランクパワーを活かせる軽いチタンフレームで、ティップ部はシングルフットを採用。</t>
         </is>
       </c>
-      <c r="AQ14" s="2" t="inlineStr"/>
+      <c r="AQ14" s="2" t="inlineStr">
+        <is>
+          <t>バリアブルテーパー / グラスコンポジット（-Gc） / バキューム / チタンフレームガイド / シングルフットティップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR14" s="2" t="inlineStr"/>
+      <c r="AS14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3121,8 +3191,13 @@
           <t>伊藤巧プロデュースの「エリートスペック」アイテム。重めのスピナーベイトやブレーデッドジグ、中型∼マグナムクランクベイトなどを扱うためのロングレングス7’3”。フルキャストしなくとも楽に飛距離を稼ぎ出し、ロングディスタンスでのバイトをしっかりとフッキングすることができます。フルグラスのティップ部はルアーをより自由に泳がせることができ、カウンターバイトにも柔らかく追従してより確実なフッキングが可能。カーボンがコンポジットされるベリーからバットエンドまでは10lbオーバーのビッグバスも余裕で制圧するパワーを誇ります。ガイドはブランクパワーを活かせる軽いチタンフレームで、ティップ部はシングルフットを採用。グリップジョイントでの2ピースブランクです。</t>
         </is>
       </c>
-      <c r="AQ15" s="2" t="inlineStr"/>
+      <c r="AQ15" s="2" t="inlineStr">
+        <is>
+          <t>バリアブルテーパー / グラスコンポジット（-Gc） / バキューム / チタンフレームガイド / シングルフットティップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー / グリップジョイント</t>
+        </is>
+      </c>
       <c r="AR15" s="2" t="inlineStr"/>
+      <c r="AS15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3263,8 +3338,13 @@
           <t>ショートロッドだから可能なアキュラシーの重要性を知るアングラーには堪らない１本。オーバーハングや複雑なカバー周りなど、一投ごとに角度やスイングを変えていくアプローチでも、ルアーをストレスなく送り込めます。ダウンジャーク、ハイジャーク、あらゆる角度でのジャーキングロッドとしてはもちろん、トップウォーターを自在に操り、クランクベイトやスピナーベイトを意のままにすり抜けさせる。さらに太めのラインと組み合わせることで、カバーを果敢に攻めるハードベイトロッドとしても優れたアイテムです。</t>
         </is>
       </c>
-      <c r="AQ16" s="2" t="inlineStr"/>
+      <c r="AQ16" s="2" t="inlineStr">
+        <is>
+          <t>バリアブルテーパー / 富士工業製GMステンレスフレームSiC-Sガイド / Kガイド / LGSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR16" s="2" t="inlineStr"/>
+      <c r="AS16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3405,8 +3485,13 @@
           <t>シャッドプラグや、スモールクランクベイトなどの軽量ルアーを、しっかりとロッドにウエイトを乗せてテクニカルキャストすることが可能。7ｇに満たない空気抵抗の大きなプラグを、低弾道なサイドやバックハンドキャストで、どんな角度からもノーミスで撃っていくために必要不可欠な柔らかさを持たせ、それでいてビッグフィッシュのファイトをしっかりと受け止めるトルクをも兼ね備えています。ハードベイトフィネスの領域を極めたいと考えているアングラーにはピッタリの一本。</t>
         </is>
       </c>
-      <c r="AQ17" s="2" t="inlineStr"/>
+      <c r="AQ17" s="2" t="inlineStr">
+        <is>
+          <t>バリアブルテーパー / 富士工業製GMステンレスフレームSiC-Sガイド / Kガイド / LGSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR17" s="2" t="inlineStr"/>
+      <c r="AS17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3547,8 +3632,13 @@
           <t>バンク沿いを流しながらショートディスタンスでピンスポットを狙っていく場合や、ロッドワークで動かすプラグに最適なアイテム。軽めのプラグでもしっかりと乗せて投げられるしなやかさがあるので、難しい角度からでもスパッとキャストが決まります。リーズや桟橋など、ワンキャストごとに狙う距離も角度も変えていくような状況でも、スキのない対応が可能。クランクベイトからトップウォーターまで、操作性を活かした釣りをしたい時にはこのロッドです。</t>
         </is>
       </c>
-      <c r="AQ18" s="2" t="inlineStr"/>
+      <c r="AQ18" s="2" t="inlineStr">
+        <is>
+          <t>バリアブルテーパー / 富士工業製GMステンレスフレームSiC-Sガイド / Kガイド / LGSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR18" s="2" t="inlineStr"/>
+      <c r="AS18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3689,8 +3779,13 @@
           <t>3/8∼1/2oz.スピナーベイトやクランクベイトなど、やや重めで引き抵抗のあるルアーをショートディスタンスで撃ち込んでいくためのロッド。引き抵抗を支える強さがありながらもキャストではしっかり曲がってくれるので、手首を回しづらいバックハンドキャストもスムーズに繰り出すことができます。粘り強さと繊細さを両立したロッドで、アシの茎を１本１本、狙えるロッドとして仕上がりました。</t>
         </is>
       </c>
-      <c r="AQ19" s="2" t="inlineStr"/>
+      <c r="AQ19" s="2" t="inlineStr">
+        <is>
+          <t>バリアブルテーパー / 富士工業製GMステンレスフレームSiC-Sガイド / Kガイド / LGSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR19" s="2" t="inlineStr"/>
+      <c r="AS19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3831,8 +3926,13 @@
           <t>「HB630L」をベースに、よりライトな領域を繊細にこなせるようにチューニングしたアイテム。小型のクランク、シャッド、トップウォーターなど従来スピニングで扱っていた7g未満のルアーを、スピニングより太いラインでカバー周りへ送り込むことが可能。また小型プラグの小さな引き抵抗でもしっかりとティップにため、水を絡ませながらリトリーブできる繊細さを備えています。ショートバイトが多発し、グラスロッドを使いたくなるような状況でも最高の性能を発揮。軽量ベイトフィネスリールとも好相性で、プラグゲームを高次元でやり込めます。</t>
         </is>
       </c>
-      <c r="AQ20" s="2" t="inlineStr"/>
+      <c r="AQ20" s="2" t="inlineStr">
+        <is>
+          <t>バリアブルテーパー / 富士工業製GMステンレスフレームSiC-Sガイド / Kガイド / LGSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR20" s="2" t="inlineStr"/>
+      <c r="AS20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3973,8 +4073,13 @@
           <t>極めてバーサタイル性の高いアイテムが「HB630L」。アキュラシーとロングキャスト、どちらもこなせる長さで、誰が使っても投げやすいテーパー。どんなレイクでも必ず使うタイプのロッドです。トップウォーター、クランクベイト、スピナーベイトなど、あらゆるハードベイトに対応し、ティップ部を回した360°キャストや、バックハンドもしっかりとこなし、汎用性の高さという点で「ハードベイトスペシャル」の最初の1本としておすすめ。バズベイトやバイブレーション、チャター系ベイトなど、リーリングベイトの乗りのよさは特筆ものです。</t>
         </is>
       </c>
-      <c r="AQ21" s="2" t="inlineStr"/>
+      <c r="AQ21" s="2" t="inlineStr">
+        <is>
+          <t>バリアブルテーパー / 富士工業製GMステンレスフレームSiC-Sガイド / Kガイド / LGSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR21" s="2" t="inlineStr"/>
+      <c r="AS21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4115,8 +4220,13 @@
           <t>1/2oz.以上のスピナーベイティングやカバークランキングで、より強さを求める上級アングラーなら、最初の1本はこちらをおすすめします。近距離でスピナーベイトをカバーにねじ込むのにも、クランクベイトやバイブレーションを使い、際どいカバー周りを太めのラインで攻め込むのにも抜群の使いやすさ。杭やスタンプを1本ずつ狙うときも、シャローフラットでバイブレーションをスローロールさせるのにも使いやすいロッドです。</t>
         </is>
       </c>
-      <c r="AQ22" s="2" t="inlineStr"/>
+      <c r="AQ22" s="2" t="inlineStr">
+        <is>
+          <t>バリアブルテーパー / 富士工業製GMステンレスフレームSiC-Sガイド / Kガイド / LGSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR22" s="2" t="inlineStr"/>
+      <c r="AS22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4257,8 +4367,13 @@
           <t>極めて高い汎用性をもち、特にジャークベイト適性の高さが光るロッド。鋭いジャーキングを作り出す適度なティップの強さ、軽いジャークベイトも無理なく飛ばせるスムーズなテーパーが高次元のジャークベイトゲームを実現。HBブランクの特性を最大限に生かし、シャロークランクから3メートルダイバーまで、ストレスのない投げ心地とミスのないフッキング性能を両立。トップウォーター、バズベイト、チャター系ベイト、スピナーベイト、バイブレーションなど、ありとあらゆるハードベイトをこなせるロッドとして、多くのアングラーから高い評価を得ています。</t>
         </is>
       </c>
-      <c r="AQ23" s="2" t="inlineStr"/>
+      <c r="AQ23" s="2" t="inlineStr">
+        <is>
+          <t>バリアブルテーパー / 富士工業製GMステンレスフレームSiC-Sガイド / Kガイド / LGSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR23" s="2" t="inlineStr"/>
+      <c r="AS23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4399,8 +4514,13 @@
           <t>インビジブルストラクチャーを一日中、正確に撃ち続けるためのロッド。そのために不可欠な、狙ったトレースコースとストライクレンジを外さないオーバーヘッドキャストの性能を追及。3/4oz.前後のスピナーベイトのスローロールや、４mダイバーのクランクベイトを集中力を切らすことなく使い続けられ、アキュラシー性を重視したベイトゲームにも対応する汎用性をも持ち合わせています。ロングキャスト性能と乗りのよさを兼ね備えたロッドです。</t>
         </is>
       </c>
-      <c r="AQ24" s="2" t="inlineStr"/>
+      <c r="AQ24" s="2" t="inlineStr">
+        <is>
+          <t>バリアブルテーパー / 富士工業製GMステンレスフレームSiC-Sガイド / Kガイド / LGSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR24" s="2" t="inlineStr"/>
+      <c r="AS24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -4541,8 +4661,13 @@
           <t>スモールクランクやフラットサイドシャロークランク、さらにはシャッドやロングビルミノーに至るまで、軽めのハードベイトもしっかりとロングキャストできるロッド。長さを活かしたポンプリトリーブもやりやすく、さらに遠いポジションからのトレースコースチェンジも思いのままにこなせるので、ウィードエリアや岩盤沿い、複数のカバーをワンキャストで攻めきる高効率な展開にもハイレベルに対応。3∼4mディープダイバーもしっかり使いこなせる、まさに理想的なクランキンロッドです。</t>
         </is>
       </c>
-      <c r="AQ25" s="2" t="inlineStr"/>
+      <c r="AQ25" s="2" t="inlineStr">
+        <is>
+          <t>バリアブルテーパー / 富士工業製GMステンレスフレームSiC-Sガイド / Kガイド / LGSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR25" s="2" t="inlineStr"/>
+      <c r="AS25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -4683,8 +4808,13 @@
           <t>ミディアムダイブクランクから3/8∼1/2oz.スピナーベイトのロングキャスト、そしてテールスピンの落とし込みからリトリーブにまで幅広い対応が可能。ペンシルベイトやプロップベイトのロングキャスト＆リッピングリトリーブ、バズベイトからスピナーベイトでの水面直下引きにまで用途は多彩。ロングロッドを使いこなせるエキスパートなら、限りなくバーサタイルなロッドに成り得ます。</t>
         </is>
       </c>
-      <c r="AQ26" s="2" t="inlineStr"/>
+      <c r="AQ26" s="2" t="inlineStr">
+        <is>
+          <t>バリアブルテーパー / 富士工業製GMステンレスフレームSiC-Sガイド / Kガイド / LGSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR26" s="2" t="inlineStr"/>
+      <c r="AS26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -4825,8 +4955,13 @@
           <t>180クラスのビッグベイト、50gクラスのマグナムクランクをはじめとした大型ルアーに適応する最強アイテム。重量のあるルアーでもサイドハンドで低弾道キャストでき、静かな着水音を作れるレングスとパワーのバランス。太軸トレブルフックのフッキングをしっかりと決める強靭なブランクでありながら、自由自在にルアーを動かせるレングスとティップバランス。ヘビーロッドだから仕方ないと諦めてしまうことなく、テクニカルな攻めを繰り出せます。パワーゲームを楽にこなす強大なトルクと、繊細な食わせを併せ持つロードランナーならではのヘビーアイテムです。</t>
         </is>
       </c>
-      <c r="AQ27" s="2" t="inlineStr"/>
+      <c r="AQ27" s="2" t="inlineStr">
+        <is>
+          <t>バリアブルテーパー / 富士工業製GMステンレスフレームSiC-Sガイド / Kガイド / LGSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR27" s="2" t="inlineStr"/>
+      <c r="AS27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -4967,8 +5102,13 @@
           <t>小型∼中型までのクランクベイトロッドとして、最高峰の使い心地と実戦的パフォーマンスを一切の妥協なく追求して両立させた、ロングクランキングロッドが「HB710LL」テレスコピック構造で強化されたバットによる十分なフッキングパワー、キャスティングの安定感を第一に考えたテーパー設計さらにリップサイズによる様々な巻き抵抗の違いをしっかりと受け止めつつ、キッチリとスラックを作り出し、深いバイトを得られる絶妙な反発力。まさに「マスター・オブ・クランキングロッド」といえる一本。</t>
         </is>
       </c>
-      <c r="AQ28" s="2" t="inlineStr"/>
+      <c r="AQ28" s="2" t="inlineStr">
+        <is>
+          <t>バリアブルテーパー / 富士工業製GMステンレスフレームSiC-Sガイド / Kガイド / LGSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー / テレスコピックハンドル</t>
+        </is>
+      </c>
       <c r="AR28" s="2" t="inlineStr"/>
+      <c r="AS28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5109,8 +5249,13 @@
           <t>ロッドによってクランクベイトの性能を拡げるのが「HB760L」。ロングキャストによって最大深度のストライクゾーンが長く取れ、シャローでは圧倒的なトレースコースチェンジによって面での攻略が可能。長さとしなやかさで高速巻きでのカウンターバイトも弾かず絡め取り、遠くの魚もしっかりフッキングできます。引き抵抗に応じて曲がりを変えるバリアブルテーパーでシャローランナーから大型ディープダイバーのフルキャスティング、スピナーベイトの高速引き。さらにはバイブレーションやスイミングジグにまで幅広く対応する中層攻略のバーサタイルロッドです。</t>
         </is>
       </c>
-      <c r="AQ29" s="2" t="inlineStr"/>
+      <c r="AQ29" s="2" t="inlineStr">
+        <is>
+          <t>バリアブルテーパー / 富士工業製GMステンレスフレームSiC-Sガイド / Kガイド / LGSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー / テレスコピックハンドル</t>
+        </is>
+      </c>
       <c r="AR29" s="2" t="inlineStr"/>
+      <c r="AS29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5251,8 +5396,13 @@
           <t>広大なディープウィードや延々と続くブレイクエッジで、大型ディープクランクやヘビースピナーベイトをフルスイングを繰り返さなくても安定的にロングキャストでき、飛距離と相まってディープを効率よくトレースすることが可能なロッド。しなやかさの中にハリのあるバットを持ち合わせているので、「ショットオーバー5」をウィードに当ててほぐして、リアクションバイトさせるテクニックには必須の１本。細い8∼10lb.ラインを使い、マックスダイブを狙ったクランキングでも、ラインの伸びを心配することなく確実にフッキングできるのもこの竿ならでは。強いフッキングの必要なスイミング系ワームやジグとも好相性。</t>
         </is>
       </c>
-      <c r="AQ30" s="2" t="inlineStr"/>
+      <c r="AQ30" s="2" t="inlineStr">
+        <is>
+          <t>バリアブルテーパー / 富士工業製GMステンレスフレームSiC-Sガイド / Kガイド / LGSTトップガイド / 富士工業製PTSリールシート / 富士工業製WBCバランサー / テレスコピックハンドル</t>
+        </is>
+      </c>
       <c r="AR30" s="2" t="inlineStr"/>
+      <c r="AS30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -5397,8 +5547,13 @@
           <t>低速から超高速巻きまで対応するシャッド専用ロッドとして設計されたのが「HB640LS-SGt」。軽量で空中回転を起こしやすいシャッドプラグを、より早いヘッドスピードとパワーでまっすぐにロングキャストできるのは、SGt（シャキットグラスティップ）を組み込んだスペシャル設計ブランクスならではのもの。超早巻きで多発するショートバイトや浅いフッキングを低減するためのSGtは、通常のカーボンロッドでは成しえない低反発を作り出し、高確率で魚をキャッチすることを可能にしました。</t>
         </is>
       </c>
-      <c r="AQ31" s="2" t="inlineStr"/>
+      <c r="AQ31" s="2" t="inlineStr">
+        <is>
+          <t>バリアブルテーパー / 富士工業製チタンフレームSiC KRコンセプトガイド / SGt（シャキットグラスティップ） / 富士工業製VSSリールシート</t>
+        </is>
+      </c>
       <c r="AR31" s="2" t="inlineStr"/>
+      <c r="AS31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -5543,8 +5698,13 @@
           <t>速い動きで低活性バスにリアクションバイトさせるメタル系ルアー。速いからこそバイトさせられるものの、それゆえにミスバイトも多いのが宿命のこの手の釣りで高確率なフッキングを可能にするのがSGt（シャキットグラスティップ）を採用したこのアイテム。鈍重と思われがちなグラスティップでありながらルアーの動きを明確に表現するシャープさを備え、それでいてグラスならではの低弾性によってバイトには素直に追従。カウンターバイトでも深く吸い込ませ、トルクのあるグラファイトバットでしっかりとフッキングに持ち込みます。PEラインと組み合わせたディープ攻略でもバラシの少ないゲームを可能にします。</t>
         </is>
       </c>
-      <c r="AQ32" s="2" t="inlineStr"/>
+      <c r="AQ32" s="2" t="inlineStr">
+        <is>
+          <t>バリアブルテーパー / 富士工業製チタンフレームSiC KRコンセプトガイド / SGt（シャキットグラスティップ） / 富士工業製VSSリールシート</t>
+        </is>
+      </c>
       <c r="AR32" s="2" t="inlineStr"/>
+      <c r="AS32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -5689,8 +5849,13 @@
           <t>ベイトタックルでも扱えるリグを、スピニング特有の繊細さでよりナチュラルに扱いバイトさせるアイテム。PE+リーダーを組み合わせ、カバーネコやダウンショット、ジグヘッドワッキーをロングキャストしてディープストラクチャーを撃つ。大きめのフックでリグるフォールベイトやノーシンカージャークをスーパーロングキャストでアプローチする。エリートプロがこだわるスピニングならではのラインの遊びが作る喰わせの間で、ビッグバスに口を使わせるアイテムです。</t>
         </is>
       </c>
-      <c r="AQ33" s="1" t="inlineStr"/>
+      <c r="AQ33" s="1" t="inlineStr">
+        <is>
+          <t>ストラクチャーNXSブランク / 富士工業製チタンフレームトルザイトガイド / KLガイド / KTガイド / 富士工業製VSSシート</t>
+        </is>
+      </c>
       <c r="AR33" s="1" t="inlineStr"/>
+      <c r="AS33" s="1" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -5835,8 +6000,13 @@
           <t>ロングキャストも、繊細な誘いも可能な長さでMLパワー、素直なテーパーでスピニングでの重めリグを一通りバーサタイルにこなせるアイテム。フロロラインで1/8oz+5インチワームのミドストやネコリグ、ジグヘッドワッキー。PE+リーダーでのムシ系カバー撃ちやオフセットネコリグでの沈み物攻め、ノーシンカーフォールベイトのロングキャストにも対応。アメリカのビッグバスと闘えるトルクフルなブランクが、日本でＰＥロングキャストフィネスとして活躍します。</t>
         </is>
       </c>
-      <c r="AQ34" s="1" t="inlineStr"/>
+      <c r="AQ34" s="1" t="inlineStr">
+        <is>
+          <t>ストラクチャーNXSブランク / 富士工業製チタンフレームトルザイトガイド / KLガイド / KTガイド / 富士工業製VSSシート</t>
+        </is>
+      </c>
       <c r="AR34" s="1" t="inlineStr"/>
+      <c r="AS34" s="1" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -5981,8 +6151,13 @@
           <t>2号クラスのPEラインと「クリオネックス」を組み合わせて空中のカバーから吊るし水面下を攻める「ツルスト」。「キャスト誤差1cm」を目標に、狙ったカバーに一投で確実に決めるために開発したショートレングスロッドが「ツルストロール」。ピッチングでのキャスト性能を最大限引き出すために敢えてパラボリックなテーパーデザインを採用し、モンスターにも負けない強靭なバットパワーも備えます。さらに小型スイッシャーや小型ポッパーでアシ際などの障害物ギリギリを攻めるテクニカルかつ隙の無いキャストも可能。プロスタッフ渡辺和哉渾身のアイテムです。</t>
         </is>
       </c>
-      <c r="AQ35" s="1" t="inlineStr"/>
+      <c r="AQ35" s="1" t="inlineStr">
+        <is>
+          <t>ストラクチャーNXSブランク / 富士工業製チタンフレームトルザイトガイド / LRVガイド / KTガイド / 富士工業製ECSリールシート</t>
+        </is>
+      </c>
       <c r="AR35" s="1" t="inlineStr"/>
+      <c r="AS35" s="1" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -6123,8 +6298,13 @@
           <t>長すぎないレングス、軽快でシャープな操作性、そして繊細さを実現する高感度が素晴らしいアイテム。5インチ前後のネコリグや1/4oz前後のドロップショットなどで杭やオダに丁寧にアプローチする時のような、食い込ませるティップの繊細さが必要で、かつ水の抵抗を受けやすいリグを操作したり障害物にリグを絡ませるための張りも欲しい攻め。そんな時に張りのあるチューブラーティップでありながら、バイトを食い込ませる柔らかさをロッド全体で作り出しているパラボリック系テーパーが活きてきます。それでいてダルさの無い仕上がりでストラクチャーNXSらしいアイテムです。</t>
         </is>
       </c>
-      <c r="AQ36" s="1" t="inlineStr"/>
+      <c r="AQ36" s="1" t="inlineStr">
+        <is>
+          <t>ストラクチャーNXSブランク / 富士工業製チタンフレームトルザイトガイド / LRVガイド / KTガイド / 富士工業製ECSリールシート</t>
+        </is>
+      </c>
       <c r="AR36" s="1" t="inlineStr"/>
+      <c r="AS36" s="1" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -6265,8 +6445,13 @@
           <t>遊びを無くした強く短いティップセクションと、ベリーからはしっかりとした張りのあるブランクが特長の1本。ヘビーテキサスでのカバー撃ちはもちろん、1/4∼5/8ozのフットボールジグをブレイクに沿わせて、思いのままに操作できる繊細さがエキスパートには堪らないアイテム。スタックが頻発するレイダウンやロックエリアでも、ウエイトに負けないティップがキレのある操作を可能にし、それでいて枝一本、ロックの凹み一つを感じ取る鋭敏さで、喰わせのタイミングを作る丁寧なコントロールを実現します。ヘビーリグを使いこなしていくためには欠かせないアイテムです</t>
         </is>
       </c>
-      <c r="AQ37" s="1" t="inlineStr"/>
+      <c r="AQ37" s="1" t="inlineStr">
+        <is>
+          <t>ストラクチャーNXSブランク / 富士工業製チタンフレームトルザイトガイド / LRVガイド / KTガイド / 富士工業製ECSリールシート</t>
+        </is>
+      </c>
       <c r="AR37" s="1" t="inlineStr"/>
+      <c r="AS37" s="1" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -6407,8 +6592,13 @@
           <t>このロッドに1/4ozシンカー、エスケープツインはどんなレイクでも欠かせないセットアップ。ベジテーションを手返し良く、揺らさず探る。フローティングカバーを遠めから静かに撃つ。消波ブロックで穴を感じ取り意図してフォール＆シェイク。ベーシックなアプローチを高度に、繊細にこなすしなやかなティップセクション。フッキングの瞬間からベリーからバットへ美しく曲がり、ロッド全体のパワーでラインブレイクする事なくランディングまで導きます。テキサス系のリグでの攻めをレベルアップさせてくれる、バーサタイルでいてスペシャルな1本です。</t>
         </is>
       </c>
-      <c r="AQ38" s="1" t="inlineStr"/>
+      <c r="AQ38" s="1" t="inlineStr">
+        <is>
+          <t>ストラクチャーNXSブランク / 富士工業製チタンフレームトルザイトガイド / LRVガイド / KTガイド / 富士工業製ECSリールシート</t>
+        </is>
+      </c>
       <c r="AR38" s="1" t="inlineStr"/>
+      <c r="AS38" s="1" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -6549,8 +6739,13 @@
           <t>ノーシンカーのフォールベイトやソフトジャークからネコリグ、ヘビダン、ライトテキサスなど標準的なソフトベイトにバーサタイル対応。ライトカバーから沖のフラットでの連続シェイクでのスイミングまでこなせるアイテム。やや長めのブランクは、カバー周りでは正確なロングピッチを繰り返すことができ、連続シェイクでは長さからくるタワミでリグを自然に泳がせ、かつ食わせの間を作り出す絶妙なバランス。ラインスラックを作りルアーを自然に漂わせた状態でのバイトも高感度ブランクで逃しません。ストラクチャーNXSの軽量セッティングで優れた操作性を生み出しているバーサタイルロッドです。</t>
         </is>
       </c>
-      <c r="AQ39" s="1" t="inlineStr"/>
+      <c r="AQ39" s="1" t="inlineStr">
+        <is>
+          <t>ストラクチャーNXSブランク / 富士工業製チタンフレームトルザイトガイド / LRVガイド / KTガイド / 富士工業製ECSリールシート</t>
+        </is>
+      </c>
       <c r="AR39" s="1" t="inlineStr"/>
+      <c r="AS39" s="1" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -6691,8 +6886,13 @@
           <t>強め長めのティップセクションでロッド全体がしなやかに曲がるモデレートテーパーの玄人好みの一本。ロングキャストしてラインが長く出ている時や、カバー絡みでクッションが効いてしまう時でもしっかりと、かつ細かくリグをコントロールできる強いティップ。その状態からでもバイトを感知する感度。しっかりとフッキングを決め、ロッドを曲げていれば自然にバスを浮かせるトルクを誇ります。ロードランナーならではの曲がりながら溢れ出るトルクがたまらないワーミングバーサタイルな一本。</t>
         </is>
       </c>
-      <c r="AQ40" s="1" t="inlineStr"/>
+      <c r="AQ40" s="1" t="inlineStr">
+        <is>
+          <t>ストラクチャーNXSブランク / 富士工業製チタンフレームトルザイトガイド / LRVガイド / KTガイド / 富士工業製ECSリールシート</t>
+        </is>
+      </c>
       <c r="AR40" s="1" t="inlineStr"/>
+      <c r="AS40" s="1" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -6833,8 +7033,13 @@
           <t>一般的な広く探る釣りとしてのキャロではなく、房総リザーバーのエキスパートが密かに繰り出すリアクションキャロライナのためのスペシャルアイテム。フラットボトムに点在するストラクチャーやブレイクエッジなどのピンスポットへ正確にリグを送り込めるキャスト性能。ヘビーシンカーをもたれることなく操作しワームを躍らせることのできるシャープなティップ。シンカーではなくリーダーの先のワームがピンスポット、さらにそのエッジを捉えたのを感知し、ビッグフィッシュが警戒しながら吸い込む瞬間をも捉える感度を誇ります。高弾性素材をメインにしながら一気にバスを浮かせるトルクを併せ持つロードランナーならではの1本です。</t>
         </is>
       </c>
-      <c r="AQ41" s="1" t="inlineStr"/>
+      <c r="AQ41" s="1" t="inlineStr">
+        <is>
+          <t>ストラクチャーNXSブランク / 富士工業製チタンフレームトルザイトガイド / LRVガイド / KTガイド / 富士工業製ECSリールシート</t>
+        </is>
+      </c>
       <c r="AR41" s="1" t="inlineStr"/>
+      <c r="AS41" s="1" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -6975,8 +7180,13 @@
           <t>高比重ノーシンカーでのベジテーション攻めや、軽めシンカーのフリーリグでの消波ブロック撃ちなど、軽いリグと太いラインを用いた繊細なアプローチのためのアイテム。7フィート2インチのレングスとは思えない操作性で軽快かつ長距離のピッチングをこなし、適度な張りを持つティップで繊細なリグコントロールと的確なバイト感知能力を備えます。軽く、シャープなブランクでありながらベリーからバットにはトルクを持たせ、柔らかく力強いフッキングが可能。スムーズなベンドカーブを描くテーパーで、低活性時の浅いフッキングでも不安なくランディングに持ち込めるテクニカルなアイテムです。</t>
         </is>
       </c>
-      <c r="AQ42" s="1" t="inlineStr"/>
+      <c r="AQ42" s="1" t="inlineStr">
+        <is>
+          <t>ストラクチャーNXSブランク / 富士工業製チタンフレームトルザイトガイド / LRVガイド / KTガイド / 富士工業製ECSリールシート / テレスコピック</t>
+        </is>
+      </c>
       <c r="AR42" s="1" t="inlineStr"/>
+      <c r="AS42" s="1" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -7117,8 +7327,13 @@
           <t>20lb.ラインを組み合わせられる強さを持ちながら、シングルハンドでの操作になんの不安も無いほどの軽快さを備えるアイテム。ヘビーカバーを撃ち続けるバルキーテキサスはもちろん、フィネスに扱いながらもパワフルなフッキングが求められるフリップギルのネコリグにもその操作性が光ります。張りとトルクをバランスさせたバットパワーは、ガード付きラバージグでのカバー越しのフッキングもしっかりと決めることができます。軽くシャープな操作性、感度も優れ、それでいてトルクフルな特性は「ストラクチャーNXS」を代表する一本です。</t>
         </is>
       </c>
-      <c r="AQ43" s="1" t="inlineStr"/>
+      <c r="AQ43" s="1" t="inlineStr">
+        <is>
+          <t>ストラクチャーNXSブランク / 富士工業製チタンフレームトルザイトガイド / LRVガイド / KTガイド / 富士工業製ECSリールシート / テレスコピック</t>
+        </is>
+      </c>
       <c r="AR43" s="1" t="inlineStr"/>
+      <c r="AS43" s="1" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -7259,8 +7474,13 @@
           <t>3インチ前後のシャッドテールなどのリアクションダウンショットや4インチ前後のネコリグ、1/8oz前後のスモラバまでの守備範囲を持つ、近年のフィッシングプレッシャーに対応するべく開発されたアイテム。絶妙な硬さに設定したソリッドティップはほんの小さなバイトにもスッと入り込み、それでいて小さな石の隙間はかわす、タフコンディション対応のコントロール性能を誇ります。ビッグフィッシュ相手でもカバーに巻かれずに引きずり出すバットパワーも持ち合わせたまさにベイトフィネススペシャルです。</t>
         </is>
       </c>
-      <c r="AQ44" s="1" t="inlineStr"/>
+      <c r="AQ44" s="1" t="inlineStr">
+        <is>
+          <t>ストラクチャーNXSブランク / 富士工業製チタンフレームトルザイトガイド / LRVガイド / KTガイド / 富士工業製ECSリールシート / ショートカーボンソリッドティップ</t>
+        </is>
+      </c>
       <c r="AR44" s="1" t="inlineStr"/>
+      <c r="AS44" s="1" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -7401,8 +7621,13 @@
           <t>カバーの奥を主戦場とし、サンカクティーサンのネコリグやカメラバなどのカバー対応ベイトの中層シェイクスペシャルです。中層という難しいレンジ攻略をいとも簡単にこなせるソリッドティップと、フッキングの瞬間にバスをカバーから引き離すバットパワーのギャップは、エキスパートをも唸らすアイテムです。軽快にヘビーカバーを撃ち抜ける絶妙な6フィート7インチのブランク長で、ベイトフィネスならではのリズミカルさを損なわずカバーを徹底攻略するアイテムです。</t>
         </is>
       </c>
-      <c r="AQ45" s="1" t="inlineStr"/>
+      <c r="AQ45" s="1" t="inlineStr">
+        <is>
+          <t>ストラクチャーNXSブランク / 富士工業製チタンフレームトルザイトガイド / LRVガイド / KTガイド / 富士工業製ECSリールシート / ショートカーボンソリッドティップ</t>
+        </is>
+      </c>
       <c r="AR45" s="1" t="inlineStr"/>
+      <c r="AS45" s="1" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -7543,8 +7768,13 @@
           <t>通常のカバー撃ちテキサスリグではバイトしてもすぐに離してしまうようなシビアなコンディションに対応すべく開発されたヘビー系ショートソリッドティップアイテム。あえて硬さを持たせたティップはエスケープツインの5gテキサスをもたれることなく操作でき、それでいてバイトの瞬間には見てわかるほど素直に曲がり込み、バスが吐き出す前にフッキングに持ち込めます。フォール中の繊細なバイトを捉えるフットボールにも対応し、ヘビーリグのソフトベイトに新たな繊細さを実現するアイテムです。</t>
         </is>
       </c>
-      <c r="AQ46" s="1" t="inlineStr"/>
+      <c r="AQ46" s="1" t="inlineStr">
+        <is>
+          <t>ストラクチャーNXSブランク / 富士工業製チタンフレームトルザイトガイド / LRVガイド / KTガイド / 富士工業製ECSリールシート / ショートカーボンソリッドティップ</t>
+        </is>
+      </c>
       <c r="AR46" s="1" t="inlineStr"/>
+      <c r="AS46" s="1" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -7685,8 +7915,13 @@
           <t>サブネームである「ニアザターゲット」の名の通り、周囲のバスを一匹たりとも逃さないために繊細な操作性と感度を極限までとことん突き詰めたロッド。0.2号クラスの極細PEラインや2ポンドクラスのフロロカーボンが多用される現代のシーンにおいて、超軽量シンカーを用いたダウンショットやネコリグ、ノーシンカーといったあらゆるライトリグの操作に対応。ディープウォーターでもボトム変化を逃さず手に取るように把握でき、その繊細さから自身の体の一部であるかのような感覚になれるアイテムです。ブランクはアンサンドフィニッシュを採用。</t>
         </is>
       </c>
-      <c r="AQ47" s="1" t="inlineStr"/>
+      <c r="AQ47" s="1" t="inlineStr">
+        <is>
+          <t>ストラクチャーNXSブランク / 富士工業製チタンフレームトルザイトガイド / KLガイド / KTガイド / 富士工業製VSSシート / アンサンドフィニッシュ</t>
+        </is>
+      </c>
       <c r="AR47" s="1" t="inlineStr"/>
+      <c r="AS47" s="1" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -7827,8 +8062,13 @@
           <t>ライトリグをミリ単位で操作する事を可能にし、突然のバイトを弾く事なく追従するティップセクション。張りのあるベリーでバイトの瞬間にタイムラグ無くバーブまで貫通させるフッキング性能。バスに主導権を与えずファイトできるバットパワー。それらを61のショートレングスの中に持ち合わせたフィネススペシャル。ノーシンカー、ダウンショット、スプリットショットなどのライトリグ全般に対応し、近年のプレッシャーに打ち勝つために作り上げられたアイテムです。</t>
         </is>
       </c>
-      <c r="AQ48" s="1" t="inlineStr"/>
+      <c r="AQ48" s="1" t="inlineStr">
+        <is>
+          <t>ストラクチャーNXSブランク / 富士工業製チタンフレームトルザイトガイド / KLガイド / KTガイド / 富士工業製VSSシート</t>
+        </is>
+      </c>
       <c r="AR48" s="1" t="inlineStr"/>
+      <c r="AS48" s="1" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -7969,8 +8209,13 @@
           <t>ボートはもちろんバンクフィッシャーマンにも強力な武器となるのが“ハイスピードフィネス”。1/16oz前後のジグヘッドやスプリットショットリグ、ダウンショット、ネコリグ、ノーシンカーなどライトリグ全般に高次元対応する汎用性を誇ります。ティップセクションはバスに食い込ませるソフトさと、リグをミリ単位で動かす操作性、シンカースタックを起こさない絶妙な張りを持たせ、ベリーから強い張りのあるエクストラファストテーパーでついばむようなバイトも一瞬で掛けていけます。「待ち」になりがちなフィネスを攻撃的に、ハイスピードにこなせる至高の一本です。</t>
         </is>
       </c>
-      <c r="AQ49" s="1" t="inlineStr"/>
+      <c r="AQ49" s="1" t="inlineStr">
+        <is>
+          <t>ストラクチャーNXSブランク / 富士工業製チタンフレームトルザイトガイド / KLガイド / KTガイド / 富士工業製VSSシート</t>
+        </is>
+      </c>
       <c r="AR49" s="1" t="inlineStr"/>
+      <c r="AS49" s="1" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -8111,8 +8356,13 @@
           <t>ラインスラックを意図的に作り出し、ジグヘッドリグやダウンショットリグを中層で漂うように泳がせる事ができる、まさにミドスト専用アイテム。ラインスラックに加えしなやかに曲がるティップからベリーがリグを跳ねさせず自然に泳がせ、柔らかくも感度に優れるブランクがバイトした瞬間を手に取るように伝えます。強めに設定したバットが素早いモーションでのフックアップを実現し、突然のビッグフィッシュも思い切ったファイトでランディングすることが可能です。</t>
         </is>
       </c>
-      <c r="AQ50" s="1" t="inlineStr"/>
+      <c r="AQ50" s="1" t="inlineStr">
+        <is>
+          <t>ストラクチャーNXSブランク / 富士工業製チタンフレームトルザイトガイド / KLガイド / KTガイド / 富士工業製VSSシート</t>
+        </is>
+      </c>
       <c r="AR50" s="1" t="inlineStr"/>
+      <c r="AS50" s="1" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -8257,8 +8507,13 @@
           <t>チューブラーブランクでありながらティップをグラス並みの低弾性カーボン、ベリーからバットを高弾性カーボンで巻き上げる製法で生まれた「Md（モーメントディレイ）」ブランク。弾性率のギャップによってティップだけをハイスピードでトゥイッチできる特性を活かし、虫をはじめとした水面系テクニックに最適なアクションが完成。細かいトゥイッチに必要なクッション性の無いPEラインとのセッティングでも、高速トゥイッチ中のバイトにも素直に追従する低弾性ティップで確実なフッキングが可能です。バットパワーはミディアムライトらしいパワフルさで、ランディング率を格段に向上させるアイテムです。</t>
         </is>
       </c>
-      <c r="AQ51" s="1" t="inlineStr"/>
+      <c r="AQ51" s="1" t="inlineStr">
+        <is>
+          <t>ストラクチャーNXSブランク / 富士工業製チタンフレームトルザイトガイド / KLガイド / KTガイド / 富士工業製VSSシート / モーメントディレイブランク</t>
+        </is>
+      </c>
       <c r="AR51" s="1" t="inlineStr"/>
+      <c r="AS51" s="1" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -8399,8 +8654,13 @@
           <t>5インチ前後のネコリグやジグヘッドワッキーなど、水の抵抗が大きめなリグも思い通りにアクションさせられる強めのティップセクションに、ロングディスタンスでもしっかりとバーブまでフックアップできるバットパワーを持ち合わせたアイテム。飛距離と操作性が両立する、6フィート5インチというレングスを活かしてのノーシンカーボイル撃ちからの高速トゥイッチや、根掛りが多発するようなバードボトムでの強めのティップを活かしたライトリグなど、汎用性の高いロングライトリグロッドです。</t>
         </is>
       </c>
-      <c r="AQ52" s="1" t="inlineStr"/>
+      <c r="AQ52" s="1" t="inlineStr">
+        <is>
+          <t>ストラクチャーNXSブランク / 富士工業製チタンフレームトルザイトガイド / KLガイド / KTガイド / 富士工業製VSSシート</t>
+        </is>
+      </c>
       <c r="AR52" s="1" t="inlineStr"/>
+      <c r="AS52" s="1" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -8541,8 +8801,13 @@
           <t>シリーズ最強のジャングルスティックを、日本のレイクにあわせデチューンしたのが「760JMH」。フリッピンロッドでなければ攻めきれないカバーの奥、ウィードクランプの中、アシやガマのインサイドを、20lb.ラインを使ったラバージグやテキサスリグ、高比重系ノーシンカーリグで狙うパワーゲーム専用ロッド。硬さの中に食わせるアソビも備えたテーパー。もちろんトルクでバスを抜く特性は、ジャングルスティックの名に恥じないものを持っています。エキスパートフリッパーなら持つべき1本。</t>
         </is>
       </c>
-      <c r="AQ53" s="2" t="inlineStr"/>
+      <c r="AQ53" s="2" t="inlineStr">
+        <is>
+          <t>テレスコピック / 富士工業製ステンレスフレームSICガイド / Kガイド / MNSTトップガイド / テレスコピックストッパー / 富士工業製TCSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR53" s="2" t="inlineStr"/>
+      <c r="AS53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -8683,8 +8948,13 @@
           <t>フリッピング専用の中でも強めで、特にウエッピングでは最強。腕力ではなくロッドのトルクでバスを引き抜くために、硬さよりもブランク自体の強さを最優先。キャストでは絶妙にウエイトを感じながらフリップでき、バスを掛けてからはロッド全体でファイトを吸収し、バラシの少ない高確率なゲームを実現。極厚ブランクは決して軽くはないものの、バランサーとのマッチングで腕に馴染むバランスが取れ、軽いロッドでは成し得ないアクションを獲得。25lb.ラインや太めのPEラインを使った1∼2oz.シンカーでのパンチングも安心して繰り出せます。</t>
         </is>
       </c>
-      <c r="AQ54" s="2" t="inlineStr"/>
+      <c r="AQ54" s="2" t="inlineStr">
+        <is>
+          <t>テレスコピック / 富士工業製ステンレスフレームSICガイド / Kガイド / MNSTトップガイド / テレスコピックストッパー / 富士工業製TCSリールシート / 富士工業製WBCバランサー</t>
+        </is>
+      </c>
       <c r="AR54" s="2" t="inlineStr"/>
+      <c r="AS54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -8829,8 +9099,13 @@
           <t>ハイプレッシャーでナーバスになり、ヘビーカバーの奥深くに隠れたビッグフィッシュを仕留めるパワーフィネス。求めたのはその攻め込みの極限。スモラバをメインとしたライトリグを、空中のカバーを突き抜けるように撃ち込むためのスピニングセッティング。ブッシュ越しでも細かくシェイクするための強いティップ。カバー対策の太いラインと太軸フックでもしっかりとフッキングできて、しかもバラシを抑える強靭なバット。高精度なピッチングを撃ち続けられるショートセパレートハンドル＆チタントルザイトガイド。「ジャングルスピン」がビッグフィッシュの安全地帯を奪います。</t>
         </is>
       </c>
-      <c r="AQ55" s="2" t="inlineStr"/>
+      <c r="AQ55" s="2" t="inlineStr">
+        <is>
+          <t>富士工業製チタンフレームトルザイトリング / KRコンセプト / 富士工業製VSSリールシート</t>
+        </is>
+      </c>
       <c r="AR55" s="2" t="inlineStr"/>
+      <c r="AS55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -8975,8 +9250,13 @@
           <t>パワーフィネスのメッカ、房総ダム群のエキスパートからの要望で生まれたのが「700JHSジャングルスピンヘビー」。まずキャストから簡単ではない使い手を選ぶ暴剣は、使いこなせば最強の剣と成り得るアイテム。680JMHSにプラス4インチし、モンスターバスを警戒させない遠投性と、高所からの吊るしでもミスらないフッキングストロークを確保。しかも１パワーアップさせたブランクをさらにファストテーパーとすることで、バイトの瞬間からフルパワーでフッキングが可能。それでいて自重は680JMHSと同等で操作性は軽快。モンスターに照準を絞ってパワーフィネスを撃ち切るエキスパート向けアイテムです。</t>
         </is>
       </c>
-      <c r="AQ56" s="2" t="inlineStr"/>
+      <c r="AQ56" s="2" t="inlineStr">
+        <is>
+          <t>富士工業製チタンフレームトルザイトリング / KRコンセプト / 富士工業製VSSリールシート</t>
+        </is>
+      </c>
       <c r="AR56" s="2" t="inlineStr"/>
+      <c r="AS56" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
